--- a/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$mod）.xlsx
+++ b/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$mod）.xlsx
@@ -59,78 +59,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;：{$mod:[value1,value2]},...}对指定字段取模，除数/被除数/余数都为整数，覆盖整数的最大和最小边界
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$mod:[value1,value2]},...}对指定字段取模，指定字段为索引字段；除数/被除数/余数都为整数，覆盖整数的最大和最小边界
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$mod:[value1,value2]},...}对指定字段取模，除数/被除数/余数都为浮点数，覆盖浮点数的最大和最小边界
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$mod:[value1,value2]},...}对指定字段取模，指定字段为索引字段；除数/被除数/余数都为浮点数，覆盖浮点数的最大和最小边界
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$mod:[value1,value2]},...}对指定字段取模，除数为数组且元素为数值型
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$mod:[value1,value2]},...}对指定字段取模，除数和被除数符号相同，覆盖（除数/被除数）：正/正、负/负，余数取被除后的有效数值
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$mod:[value1,value2]},...}对指定字段取模，除数和被除数符号不同，覆盖（除数/被除数）：正/负、负/正，余数取被除后的有效数值
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、查询成功，取模后返回结果正确，匹配记录包括数值和符号均正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;：{$mod:[value1,value2]},...}对指定字段取模，指定字段为索引字段；除数为数组且元素为数值型
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$mod:[value1,value2]},...}对指定字段取模，除数为0，被除数取任意数值，余数取0
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、查询成功，返回与匹配条件匹配的记录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;：{$mod:[value1,value2]},...}对指定字段取模，被除数为0
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、查询失败，被除数不能取0，提示信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;：{$mod:[value1,value2]},...}对指定字段取模，被除数为小于1的小数（如0.1），余数取被除后的有效数值
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;：{$mod:[value1,value2]},...}对指定字段取模，除数为其他类型数据（如timestamp）
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、查询成功，小数时系统自动取整，查询后返回结果集正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -173,6 +113,54 @@
   </si>
   <si>
     <t>使用$mod查询，除数为其他类型数据</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$mod:[value1,value2]},...})对指定字段取模，除数/被除数/余数都为整数，覆盖整数的最大和最小边界
+2、检查查询结果正确性</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$mod:[value1,value2]},...})对指定字段取模，指定字段为索引字段；除数/被除数/余数都为整数，覆盖整数的最大和最小边界
+2、检查查询结果正确性</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$mod:[value1,value2]},...})对指定字段取模，除数/被除数/余数都为浮点数，覆盖浮点数的最大和最小边界
+2、检查查询结果正确性</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$mod:[value1,value2]},...})对指定字段取模，指定字段为索引字段；除数/被除数/余数都为浮点数，覆盖浮点数的最大和最小边界
+2、检查查询结果正确性</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$mod:[value1,value2]},...})对指定字段取模，除数为数组且元素为数值型
+2、检查查询结果正确性</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$mod:[value1,value2]},...})对指定字段取模，指定字段为索引字段；除数为数组且元素为数值型
+2、检查查询结果正确性</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$mod:[value1,value2]},...})对指定字段取模，除数和被除数符号相同，覆盖（除数/被除数）：正/正、负/负，余数取被除后的有效数值
+2、检查查询结果正确性</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$mod:[value1,value2]},...})对指定字段取模，除数和被除数符号不同，覆盖（除数/被除数）：正/负、负/正，余数取被除后的有效数值
+2、检查查询结果正确性</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$mod:[value1,value2]},...})对指定字段取模，除数为0，被除数取任意数值，余数取0
+2、检查查询结果正确性</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$mod:[value1,value2]},...})对指定字段取模，被除数为0
+2、检查查询结果正确性</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$mod:[value1,value2]},...})对指定字段取模，被除数为小于1的小数（如0.1），余数取被除后的有效数值
+2、检查查询结果正确性</t>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;：{$mod:[value1,value2]},...})对指定字段取模，除数为其他类型数据（如timestamp）
+2、检查查询结果正确性</t>
   </si>
 </sst>
 </file>
@@ -682,7 +670,7 @@
     </row>
     <row r="2" spans="1:9" ht="94.5">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>10</v>
@@ -700,10 +688,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I2" s="3">
         <v>1</v>
@@ -711,25 +699,25 @@
     </row>
     <row r="3" spans="1:9" ht="54">
       <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
@@ -737,25 +725,25 @@
     </row>
     <row r="4" spans="1:9" ht="54">
       <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
@@ -763,25 +751,25 @@
     </row>
     <row r="5" spans="1:9" ht="54">
       <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>2</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -789,25 +777,25 @@
     </row>
     <row r="6" spans="1:9" ht="40.5">
       <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
@@ -815,25 +803,25 @@
     </row>
     <row r="7" spans="1:9" ht="54">
       <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I7" s="3">
         <v>1</v>
@@ -841,144 +829,144 @@
     </row>
     <row r="8" spans="1:9" ht="54">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:9" ht="54">
       <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:9" ht="40.5">
       <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I10" s="3"/>
     </row>
     <row r="11" spans="1:9" ht="40.5">
       <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3">
-        <v>2</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9" ht="54">
       <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3">
-        <v>2</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="40.5">
       <c r="A13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
